--- a/output/roomself_excel/13124.xlsx
+++ b/output/roomself_excel/13124.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>122801</v>
+        <v>253503</v>
       </c>
       <c r="D2" t="n">
-        <v>2808</v>
+        <v>5700</v>
       </c>
       <c r="E2" t="n">
-        <v>396</v>
+        <v>863</v>
       </c>
       <c r="F2" t="n">
-        <v>358</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36581</v>
+        <v>122801</v>
       </c>
       <c r="D3" t="n">
-        <v>1560</v>
+        <v>2808</v>
       </c>
       <c r="E3" t="n">
-        <v>157</v>
+        <v>396</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29591</v>
+        <v>103826</v>
       </c>
       <c r="D4" t="n">
-        <v>1440</v>
+        <v>2736</v>
       </c>
       <c r="E4" t="n">
-        <v>127</v>
+        <v>307</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47688</v>
+        <v>108041</v>
       </c>
       <c r="D5" t="n">
-        <v>1812</v>
+        <v>2660</v>
       </c>
       <c r="E5" t="n">
-        <v>491</v>
+        <v>340</v>
       </c>
       <c r="F5" t="n">
-        <v>233</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44655</v>
+        <v>29591</v>
       </c>
       <c r="D6" t="n">
-        <v>1696</v>
+        <v>1440</v>
       </c>
       <c r="E6" t="n">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="F6" t="n">
-        <v>220</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55533</v>
+        <v>47688</v>
       </c>
       <c r="D7" t="n">
-        <v>1976</v>
+        <v>1812</v>
       </c>
       <c r="E7" t="n">
-        <v>435</v>
+        <v>220</v>
       </c>
       <c r="F7" t="n">
-        <v>285</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>498363</v>
+        <v>22326</v>
       </c>
       <c r="D8" t="n">
-        <v>10052</v>
+        <v>1220</v>
       </c>
       <c r="E8" t="n">
-        <v>1526</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103826</v>
+        <v>79313</v>
       </c>
       <c r="D9" t="n">
-        <v>2736</v>
+        <v>2716</v>
       </c>
       <c r="E9" t="n">
-        <v>307</v>
+        <v>153</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>108041</v>
+        <v>36581</v>
       </c>
       <c r="D10" t="n">
-        <v>2660</v>
+        <v>1560</v>
       </c>
       <c r="E10" t="n">
-        <v>676</v>
+        <v>157</v>
       </c>
       <c r="F10" t="n">
-        <v>286</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22326</v>
+        <v>343180</v>
       </c>
       <c r="D11" t="n">
-        <v>1220</v>
+        <v>4692</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>586</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>343180</v>
+        <v>44655</v>
       </c>
       <c r="D12" t="n">
-        <v>4692</v>
+        <v>1696</v>
       </c>
       <c r="E12" t="n">
-        <v>630</v>
+        <v>260</v>
       </c>
       <c r="F12" t="n">
-        <v>586</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
@@ -712,15 +712,59 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>55533</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1976</v>
+      </c>
+      <c r="E13" t="n">
+        <v>435</v>
+      </c>
+      <c r="F13" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>165547</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3425</v>
+      </c>
+      <c r="E14" t="n">
+        <v>436</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>151658</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D15" t="n">
         <v>3204</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" t="n">
         <v>550</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>336</v>
       </c>
     </row>

--- a/output/roomself_excel/13124.xlsx
+++ b/output/roomself_excel/13124.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>5700</v>
       </c>
-      <c r="E2" t="n">
-        <v>863</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>643</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,31 @@
       <c r="D3" t="n">
         <v>2808</v>
       </c>
-      <c r="E3" t="n">
-        <v>396</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>358</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>371</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +584,23 @@
       <c r="D4" t="n">
         <v>2736</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>307</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>27</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +617,31 @@
       <c r="D5" t="n">
         <v>2660</v>
       </c>
-      <c r="E5" t="n">
-        <v>340</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>286</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>282</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,23 @@
       <c r="D6" t="n">
         <v>1440</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>127</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>25</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +691,23 @@
       <c r="D7" t="n">
         <v>1812</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>220</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>25</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,15 @@
       <c r="D8" t="n">
         <v>1220</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +749,23 @@
       <c r="D9" t="n">
         <v>2716</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>153</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>28</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +782,23 @@
       <c r="D10" t="n">
         <v>1560</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>157</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>25</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +815,38 @@
       <c r="D11" t="n">
         <v>4692</v>
       </c>
-      <c r="E11" t="n">
-        <v>630</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>586</v>
+        <v>195</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>575</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>335</v>
+      </c>
+      <c r="M11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +864,31 @@
       <c r="D12" t="n">
         <v>1696</v>
       </c>
-      <c r="E12" t="n">
-        <v>260</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>220</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>195</v>
+      </c>
+      <c r="J12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +905,31 @@
       <c r="D13" t="n">
         <v>1976</v>
       </c>
-      <c r="E13" t="n">
-        <v>435</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>285</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="G13" t="n">
+        <v>31</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>254</v>
+      </c>
+      <c r="J13" t="n">
+        <v>29</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +946,23 @@
       <c r="D14" t="n">
         <v>3425</v>
       </c>
-      <c r="E14" t="n">
-        <v>436</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +979,38 @@
       <c r="D15" t="n">
         <v>3204</v>
       </c>
-      <c r="E15" t="n">
-        <v>550</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>336</v>
+        <v>307</v>
+      </c>
+      <c r="G15" t="n">
+        <v>27</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>307</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>494</v>
+      </c>
+      <c r="M15" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
